--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -17827,10 +17827,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>118338779</v>
+        <v>118338786</v>
       </c>
       <c r="B149" t="n">
-        <v>90031</v>
+        <v>90039</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17839,25 +17839,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5733</v>
+        <v>5747</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Såpfingersvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Ramaria lutea</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Vent.) Schild</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -17870,10 +17870,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>705841</v>
+        <v>706002</v>
       </c>
       <c r="R149" t="n">
-        <v>6634776</v>
+        <v>6634692</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17905,7 +17905,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -17915,12 +17915,12 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Kollekt B234.</t>
+          <t>Kollekt MAx-B233.</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -18077,10 +18077,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>118338786</v>
+        <v>118338779</v>
       </c>
       <c r="B151" t="n">
-        <v>90039</v>
+        <v>90031</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -18089,25 +18089,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5747</v>
+        <v>5733</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(Vent.) Schild</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -18120,10 +18120,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>706002</v>
+        <v>705841</v>
       </c>
       <c r="R151" t="n">
-        <v>6634692</v>
+        <v>6634776</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -18155,7 +18155,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -18165,12 +18165,12 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Kollekt MAx-B233.</t>
+          <t>Kollekt B234.</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -18202,10 +18202,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>118815308</v>
+        <v>118815166</v>
       </c>
       <c r="B152" t="n">
-        <v>90031</v>
+        <v>90039</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -18214,25 +18214,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5733</v>
+        <v>5747</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Såpfingersvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Ramaria lutea</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Vent.) Schild</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -18241,17 +18241,17 @@
       <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Haggård (Haggård), Upl</t>
+          <t>Haggård, Upl</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>705930</v>
+        <v>706024</v>
       </c>
       <c r="R152" t="n">
-        <v>6634874</v>
+        <v>6634889</v>
       </c>
       <c r="S152" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -18280,7 +18280,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -18290,12 +18290,12 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Kollekt B184.</t>
+          <t>Kollekt 195.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18327,10 +18327,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>118815166</v>
+        <v>118815308</v>
       </c>
       <c r="B153" t="n">
-        <v>90039</v>
+        <v>90031</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -18339,25 +18339,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5747</v>
+        <v>5733</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(Vent.) Schild</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -18366,17 +18366,17 @@
       <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Haggård, Upl</t>
+          <t>Haggård (Haggård), Upl</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>706024</v>
+        <v>705930</v>
       </c>
       <c r="R153" t="n">
-        <v>6634889</v>
+        <v>6634874</v>
       </c>
       <c r="S153" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -18405,7 +18405,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -18415,12 +18415,12 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Kollekt 195.</t>
+          <t>Kollekt B184.</t>
         </is>
       </c>
       <c r="AD153" t="b">

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -17827,10 +17827,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>118338786</v>
+        <v>118338782</v>
       </c>
       <c r="B149" t="n">
-        <v>90039</v>
+        <v>90031</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17839,25 +17839,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5747</v>
+        <v>5733</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(Vent.) Schild</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -17870,10 +17870,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>706002</v>
+        <v>705947</v>
       </c>
       <c r="R149" t="n">
-        <v>6634692</v>
+        <v>6634844</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17900,27 +17900,27 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Kollekt MAx-B233.</t>
+          <t>Kollekt B188.</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17952,10 +17952,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>118338782</v>
+        <v>118338786</v>
       </c>
       <c r="B150" t="n">
-        <v>90031</v>
+        <v>90039</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17964,25 +17964,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5733</v>
+        <v>5747</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Såpfingersvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Ramaria lutea</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Vent.) Schild</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -17995,10 +17995,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>705947</v>
+        <v>706002</v>
       </c>
       <c r="R150" t="n">
-        <v>6634844</v>
+        <v>6634692</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -18025,27 +18025,27 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Kollekt B188.</t>
+          <t>Kollekt MAx-B233.</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -18202,10 +18202,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>118815166</v>
+        <v>118815308</v>
       </c>
       <c r="B152" t="n">
-        <v>90039</v>
+        <v>90031</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -18214,25 +18214,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5747</v>
+        <v>5733</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(Vent.) Schild</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -18241,17 +18241,17 @@
       <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Haggård, Upl</t>
+          <t>Haggård (Haggård), Upl</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>706024</v>
+        <v>705930</v>
       </c>
       <c r="R152" t="n">
-        <v>6634889</v>
+        <v>6634874</v>
       </c>
       <c r="S152" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -18280,7 +18280,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -18290,12 +18290,12 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Kollekt 195.</t>
+          <t>Kollekt B184.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18327,10 +18327,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>118815308</v>
+        <v>118815166</v>
       </c>
       <c r="B153" t="n">
-        <v>90031</v>
+        <v>90039</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -18339,25 +18339,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5733</v>
+        <v>5747</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Såpfingersvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Ramaria lutea</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Vent.) Schild</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -18366,17 +18366,17 @@
       <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Haggård (Haggård), Upl</t>
+          <t>Haggård, Upl</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>705930</v>
+        <v>706024</v>
       </c>
       <c r="R153" t="n">
-        <v>6634874</v>
+        <v>6634889</v>
       </c>
       <c r="S153" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -18405,7 +18405,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -18415,12 +18415,12 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Kollekt B184.</t>
+          <t>Kollekt 195.</t>
         </is>
       </c>
       <c r="AD153" t="b">

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -17827,10 +17827,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>118338782</v>
+        <v>118338786</v>
       </c>
       <c r="B149" t="n">
-        <v>90031</v>
+        <v>90046</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17839,25 +17839,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5733</v>
+        <v>5747</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Såpfingersvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Ramaria lutea</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Vent.) Schild</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -17870,10 +17870,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>705947</v>
+        <v>706002</v>
       </c>
       <c r="R149" t="n">
-        <v>6634844</v>
+        <v>6634692</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17900,27 +17900,27 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Kollekt B188.</t>
+          <t>Kollekt MAx-B233.</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17952,10 +17952,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>118338786</v>
+        <v>118338782</v>
       </c>
       <c r="B150" t="n">
-        <v>90039</v>
+        <v>90038</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17964,25 +17964,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5747</v>
+        <v>5733</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(Vent.) Schild</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -17995,10 +17995,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>706002</v>
+        <v>705947</v>
       </c>
       <c r="R150" t="n">
-        <v>6634692</v>
+        <v>6634844</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -18025,27 +18025,27 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Kollekt MAx-B233.</t>
+          <t>Kollekt B188.</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -18080,7 +18080,7 @@
         <v>118338779</v>
       </c>
       <c r="B151" t="n">
-        <v>90031</v>
+        <v>90038</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>118815308</v>
       </c>
       <c r="B152" t="n">
-        <v>90031</v>
+        <v>90038</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>118815166</v>
       </c>
       <c r="B153" t="n">
-        <v>90039</v>
+        <v>90046</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -18202,10 +18202,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>118815308</v>
+        <v>118815166</v>
       </c>
       <c r="B152" t="n">
-        <v>90038</v>
+        <v>90046</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -18214,25 +18214,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5733</v>
+        <v>5747</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Såpfingersvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Ramaria lutea</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Vent.) Schild</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -18241,17 +18241,17 @@
       <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Haggård (Haggård), Upl</t>
+          <t>Haggård, Upl</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>705930</v>
+        <v>706024</v>
       </c>
       <c r="R152" t="n">
-        <v>6634874</v>
+        <v>6634889</v>
       </c>
       <c r="S152" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -18280,7 +18280,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -18290,12 +18290,12 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Kollekt B184.</t>
+          <t>Kollekt 195.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18327,10 +18327,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>118815166</v>
+        <v>118815308</v>
       </c>
       <c r="B153" t="n">
-        <v>90046</v>
+        <v>90038</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -18339,25 +18339,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5747</v>
+        <v>5733</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(Vent.) Schild</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -18366,17 +18366,17 @@
       <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Haggård, Upl</t>
+          <t>Haggård (Haggård), Upl</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>706024</v>
+        <v>705930</v>
       </c>
       <c r="R153" t="n">
-        <v>6634889</v>
+        <v>6634874</v>
       </c>
       <c r="S153" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -18405,7 +18405,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -18415,12 +18415,12 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Kollekt 195.</t>
+          <t>Kollekt B184.</t>
         </is>
       </c>
       <c r="AD153" t="b">

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -11787,7 +11787,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY180"/>
+  <dimension ref="A1:AY181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15591,7 +15591,7 @@
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>Svampar i Roslagen</t>
+          <t>Svampar i Roslagen, Fynd med DNA-sekvens - extern</t>
         </is>
       </c>
     </row>
@@ -21762,6 +21762,121 @@
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>120295821</v>
+      </c>
+      <c r="B181" t="n">
+        <v>90089</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>5733</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Såpfingersvamp</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Ramaria lutea</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>(Vent.) Schild</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>Haggård, Upl</t>
+        </is>
+      </c>
+      <c r="Q181" t="n">
+        <v>706011</v>
+      </c>
+      <c r="R181" t="n">
+        <v>6634895</v>
+      </c>
+      <c r="S181" t="n">
+        <v>10</v>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>2023-09-16</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>2023-09-16</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>MAx-B227</t>
+        </is>
+      </c>
+      <c r="AD181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF181" t="inlineStr"/>
+      <c r="AG181" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT181" t="inlineStr"/>
+      <c r="AW181" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX181" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY181" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen, Fynd med DNA-sekvens - extern</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -1630,7 +1630,7 @@
         <v>112212372</v>
       </c>
       <c r="B10" t="n">
-        <v>90052</v>
+        <v>90069</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>112212050</v>
       </c>
       <c r="B11" t="n">
-        <v>91842</v>
+        <v>91860</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>112212264</v>
       </c>
       <c r="B12" t="n">
-        <v>90097</v>
+        <v>90114</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>112212023</v>
       </c>
       <c r="B13" t="n">
-        <v>90097</v>
+        <v>90114</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>112211954</v>
       </c>
       <c r="B14" t="n">
-        <v>91254</v>
+        <v>91272</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>112212332</v>
       </c>
       <c r="B15" t="n">
-        <v>91832</v>
+        <v>91850</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>112211957</v>
       </c>
       <c r="B16" t="n">
-        <v>91832</v>
+        <v>91850</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>112212357</v>
       </c>
       <c r="B18" t="n">
-        <v>91829</v>
+        <v>91847</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>112212020</v>
       </c>
       <c r="B19" t="n">
-        <v>90075</v>
+        <v>90092</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>112211995</v>
       </c>
       <c r="B22" t="n">
-        <v>86379</v>
+        <v>86396</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>112212091</v>
       </c>
       <c r="B23" t="n">
-        <v>90846</v>
+        <v>90864</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>112212315</v>
       </c>
       <c r="B24" t="n">
-        <v>91848</v>
+        <v>91866</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>112212352</v>
       </c>
       <c r="B27" t="n">
-        <v>89212</v>
+        <v>89229</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>112211999</v>
       </c>
       <c r="B28" t="n">
-        <v>86453</v>
+        <v>86470</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>112212097</v>
       </c>
       <c r="B39" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>112212360</v>
       </c>
       <c r="B40" t="n">
-        <v>90052</v>
+        <v>90069</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>112212003</v>
       </c>
       <c r="B41" t="n">
-        <v>90061</v>
+        <v>90078</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>112212245</v>
       </c>
       <c r="B45" t="n">
-        <v>86409</v>
+        <v>86426</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>112212324</v>
       </c>
       <c r="B55" t="n">
-        <v>90097</v>
+        <v>90114</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         <v>112212276</v>
       </c>
       <c r="B56" t="n">
-        <v>90106</v>
+        <v>90123</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>112212039</v>
       </c>
       <c r="B62" t="n">
-        <v>90097</v>
+        <v>90114</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         <v>112212343</v>
       </c>
       <c r="B70" t="n">
-        <v>91848</v>
+        <v>91866</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>112212028</v>
       </c>
       <c r="B71" t="n">
-        <v>91832</v>
+        <v>91850</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>112212291</v>
       </c>
       <c r="B72" t="n">
-        <v>91852</v>
+        <v>91870</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>112211976</v>
       </c>
       <c r="B75" t="n">
-        <v>86397</v>
+        <v>86414</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>112215302</v>
       </c>
       <c r="B81" t="n">
-        <v>86469</v>
+        <v>86486</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         <v>112212058</v>
       </c>
       <c r="B91" t="n">
-        <v>91832</v>
+        <v>91850</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>112212358</v>
       </c>
       <c r="B92" t="n">
-        <v>90106</v>
+        <v>90123</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>112256851</v>
       </c>
       <c r="B95" t="n">
-        <v>91848</v>
+        <v>91866</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
         <v>112258193</v>
       </c>
       <c r="B96" t="n">
-        <v>90043</v>
+        <v>90060</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         <v>112257213</v>
       </c>
       <c r="B97" t="n">
-        <v>90075</v>
+        <v>90092</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         <v>112258206</v>
       </c>
       <c r="B98" t="n">
-        <v>86342</v>
+        <v>86359</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>112257866</v>
       </c>
       <c r="B99" t="n">
-        <v>86432</v>
+        <v>86449</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         <v>112257802</v>
       </c>
       <c r="B100" t="n">
-        <v>91547</v>
+        <v>91565</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>112256808</v>
       </c>
       <c r="B101" t="n">
-        <v>91861</v>
+        <v>91879</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12598,7 +12598,7 @@
         <v>112257684</v>
       </c>
       <c r="B102" t="n">
-        <v>91306</v>
+        <v>91324</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12720,7 +12720,7 @@
         <v>112258061</v>
       </c>
       <c r="B103" t="n">
-        <v>91182</v>
+        <v>91200</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12837,7 +12837,7 @@
         <v>112257509</v>
       </c>
       <c r="B104" t="n">
-        <v>86397</v>
+        <v>86414</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
         <v>112256783</v>
       </c>
       <c r="B105" t="n">
-        <v>91494</v>
+        <v>91512</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -13071,7 +13071,7 @@
         <v>112257311</v>
       </c>
       <c r="B106" t="n">
-        <v>86205</v>
+        <v>86222</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -13188,7 +13188,7 @@
         <v>112257145</v>
       </c>
       <c r="B107" t="n">
-        <v>91848</v>
+        <v>91866</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>112309343</v>
       </c>
       <c r="B108" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>112313829</v>
       </c>
       <c r="B109" t="n">
-        <v>90052</v>
+        <v>90069</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>112257092</v>
       </c>
       <c r="B110" t="n">
-        <v>89212</v>
+        <v>89229</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13655,7 +13655,7 @@
         <v>112310429</v>
       </c>
       <c r="B111" t="n">
-        <v>86205</v>
+        <v>86222</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         <v>112313201</v>
       </c>
       <c r="B112" t="n">
-        <v>91832</v>
+        <v>91850</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>112309124</v>
       </c>
       <c r="B113" t="n">
-        <v>91494</v>
+        <v>91512</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>112310552</v>
       </c>
       <c r="B114" t="n">
-        <v>86432</v>
+        <v>86449</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>112309411</v>
       </c>
       <c r="B115" t="n">
-        <v>86397</v>
+        <v>86414</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>112320037</v>
       </c>
       <c r="B116" t="n">
-        <v>91262</v>
+        <v>91280</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
         <v>112314464</v>
       </c>
       <c r="B117" t="n">
-        <v>91861</v>
+        <v>91879</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>112309581</v>
       </c>
       <c r="B118" t="n">
-        <v>86432</v>
+        <v>86449</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14561,7 +14561,7 @@
         <v>112319539</v>
       </c>
       <c r="B119" t="n">
-        <v>89193</v>
+        <v>89210</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>112309519</v>
       </c>
       <c r="B120" t="n">
-        <v>90075</v>
+        <v>90092</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>112312232</v>
       </c>
       <c r="B121" t="n">
-        <v>90089</v>
+        <v>90106</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14920,7 +14920,7 @@
         <v>112309070</v>
       </c>
       <c r="B122" t="n">
-        <v>86397</v>
+        <v>86414</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15037,7 +15037,7 @@
         <v>112310528</v>
       </c>
       <c r="B123" t="n">
-        <v>91861</v>
+        <v>91879</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>112309877</v>
       </c>
       <c r="B124" t="n">
-        <v>91832</v>
+        <v>91850</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>112309475</v>
       </c>
       <c r="B125" t="n">
-        <v>86205</v>
+        <v>86222</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>112314048</v>
       </c>
       <c r="B126" t="n">
-        <v>86205</v>
+        <v>86222</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -15475,7 +15475,7 @@
         <v>112315113</v>
       </c>
       <c r="B127" t="n">
-        <v>90089</v>
+        <v>90106</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>112308853</v>
       </c>
       <c r="B128" t="n">
-        <v>90334</v>
+        <v>90351</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>112310654</v>
       </c>
       <c r="B129" t="n">
-        <v>86308</v>
+        <v>86325</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>112309786</v>
       </c>
       <c r="B130" t="n">
-        <v>87320</v>
+        <v>87337</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15941,7 +15941,7 @@
         <v>112308815</v>
       </c>
       <c r="B131" t="n">
-        <v>91861</v>
+        <v>91879</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -16058,7 +16058,7 @@
         <v>112313523</v>
       </c>
       <c r="B132" t="n">
-        <v>91832</v>
+        <v>91850</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -16165,7 +16165,7 @@
         <v>112309206</v>
       </c>
       <c r="B133" t="n">
-        <v>86205</v>
+        <v>86222</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>112313173</v>
       </c>
       <c r="B134" t="n">
-        <v>91852</v>
+        <v>91870</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -16389,7 +16389,7 @@
         <v>112313514</v>
       </c>
       <c r="B135" t="n">
-        <v>86432</v>
+        <v>86449</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>112312127</v>
       </c>
       <c r="B136" t="n">
-        <v>90075</v>
+        <v>90092</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>112309911</v>
       </c>
       <c r="B137" t="n">
-        <v>90075</v>
+        <v>90092</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -16710,7 +16710,7 @@
         <v>112309002</v>
       </c>
       <c r="B138" t="n">
-        <v>90097</v>
+        <v>90114</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16835,7 +16835,7 @@
         <v>112313926</v>
       </c>
       <c r="B139" t="n">
-        <v>86205</v>
+        <v>86222</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>112314024</v>
       </c>
       <c r="B140" t="n">
-        <v>91832</v>
+        <v>91850</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -17049,7 +17049,7 @@
         <v>112314853</v>
       </c>
       <c r="B141" t="n">
-        <v>86432</v>
+        <v>86449</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -18394,7 +18394,7 @@
         <v>118338786</v>
       </c>
       <c r="B152" t="n">
-        <v>90097</v>
+        <v>90114</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
         <v>118338782</v>
       </c>
       <c r="B153" t="n">
-        <v>90089</v>
+        <v>90106</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -18644,7 +18644,7 @@
         <v>118338779</v>
       </c>
       <c r="B154" t="n">
-        <v>90089</v>
+        <v>90106</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -18769,7 +18769,7 @@
         <v>118815166</v>
       </c>
       <c r="B155" t="n">
-        <v>90097</v>
+        <v>90114</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>118815308</v>
       </c>
       <c r="B156" t="n">
-        <v>90089</v>
+        <v>90106</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>120295821</v>
       </c>
       <c r="B181" t="n">
-        <v>90089</v>
+        <v>90106</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY181"/>
+  <dimension ref="A1:AY185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21877,6 +21877,430 @@
         </is>
       </c>
     </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>120521492</v>
+      </c>
+      <c r="B182" t="n">
+        <v>86222</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>Rantet, Upl</t>
+        </is>
+      </c>
+      <c r="Q182" t="n">
+        <v>705979</v>
+      </c>
+      <c r="R182" t="n">
+        <v>6634871</v>
+      </c>
+      <c r="S182" t="n">
+        <v>4</v>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF182" t="inlineStr"/>
+      <c r="AG182" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT182" t="inlineStr"/>
+      <c r="AW182" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX182" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>120521743</v>
+      </c>
+      <c r="B183" t="n">
+        <v>91512</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>Rantet, Upl</t>
+        </is>
+      </c>
+      <c r="Q183" t="n">
+        <v>705982</v>
+      </c>
+      <c r="R183" t="n">
+        <v>6634774</v>
+      </c>
+      <c r="S183" t="n">
+        <v>10</v>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF183" t="inlineStr"/>
+      <c r="AG183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT183" t="inlineStr"/>
+      <c r="AW183" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX183" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>120521723</v>
+      </c>
+      <c r="B184" t="n">
+        <v>91870</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>Rantet, Upl</t>
+        </is>
+      </c>
+      <c r="Q184" t="n">
+        <v>705982</v>
+      </c>
+      <c r="R184" t="n">
+        <v>6634774</v>
+      </c>
+      <c r="S184" t="n">
+        <v>10</v>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF184" t="inlineStr"/>
+      <c r="AG184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT184" t="inlineStr"/>
+      <c r="AW184" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX184" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>120521829</v>
+      </c>
+      <c r="B185" t="n">
+        <v>86222</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>Rantet, Upl</t>
+        </is>
+      </c>
+      <c r="Q185" t="n">
+        <v>706011</v>
+      </c>
+      <c r="R185" t="n">
+        <v>6634735</v>
+      </c>
+      <c r="S185" t="n">
+        <v>10</v>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>2024-10-20</t>
+        </is>
+      </c>
+      <c r="AD185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF185" t="inlineStr"/>
+      <c r="AG185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT185" t="inlineStr"/>
+      <c r="AW185" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX185" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Joakim Ekman, Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY185" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -21879,10 +21879,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>120521492</v>
+        <v>120521743</v>
       </c>
       <c r="B182" t="n">
-        <v>86222</v>
+        <v>91512</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -21895,21 +21895,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>3762</v>
+        <v>4769</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -21922,13 +21922,13 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>705979</v>
+        <v>705982</v>
       </c>
       <c r="R182" t="n">
-        <v>6634871</v>
+        <v>6634774</v>
       </c>
       <c r="S182" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -21985,10 +21985,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>120521743</v>
+        <v>120521723</v>
       </c>
       <c r="B183" t="n">
-        <v>91512</v>
+        <v>91870</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -22001,21 +22001,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>4769</v>
+        <v>4366</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -22091,10 +22091,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>120521723</v>
+        <v>120521829</v>
       </c>
       <c r="B184" t="n">
-        <v>91870</v>
+        <v>86222</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -22107,21 +22107,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>4366</v>
+        <v>3762</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -22134,10 +22134,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>705982</v>
+        <v>706011</v>
       </c>
       <c r="R184" t="n">
-        <v>6634774</v>
+        <v>6634735</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -22197,7 +22197,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>120521829</v>
+        <v>120521492</v>
       </c>
       <c r="B185" t="n">
         <v>86222</v>
@@ -22240,13 +22240,13 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>706011</v>
+        <v>705979</v>
       </c>
       <c r="R185" t="n">
-        <v>6634735</v>
+        <v>6634871</v>
       </c>
       <c r="S185" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY185"/>
+  <dimension ref="A1:AY186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6522,7 +6522,7 @@
         <v>112129200</v>
       </c>
       <c r="B51" t="n">
-        <v>90220</v>
+        <v>90230</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>119058657</v>
       </c>
       <c r="B169" t="n">
-        <v>91971</v>
+        <v>91981</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -21549,7 +21549,7 @@
         <v>119130129</v>
       </c>
       <c r="B179" t="n">
-        <v>90089</v>
+        <v>90225</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -21580,6 +21580,9 @@
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Haggård, Upl</t>
@@ -21630,6 +21633,7 @@
       <c r="AE179" t="b">
         <v>0</v>
       </c>
+      <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="b">
         <v>0</v>
       </c>
@@ -21644,7 +21648,11 @@
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY179" t="inlineStr"/>
+      <c r="AY179" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -22301,6 +22309,112 @@
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>121408711</v>
+      </c>
+      <c r="B186" t="n">
+        <v>91683</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>5836</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Guldkremla</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Russula aurea</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>Haggård, Upl</t>
+        </is>
+      </c>
+      <c r="Q186" t="n">
+        <v>705971</v>
+      </c>
+      <c r="R186" t="n">
+        <v>6634882</v>
+      </c>
+      <c r="S186" t="n">
+        <v>10</v>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="AD186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT186" t="inlineStr"/>
+      <c r="AW186" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX186" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY186" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -6522,7 +6522,7 @@
         <v>112129200</v>
       </c>
       <c r="B51" t="n">
-        <v>90230</v>
+        <v>90242</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>119058657</v>
       </c>
       <c r="B169" t="n">
-        <v>91981</v>
+        <v>91993</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -21549,7 +21549,7 @@
         <v>119130129</v>
       </c>
       <c r="B179" t="n">
-        <v>90225</v>
+        <v>90237</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -22314,7 +22314,7 @@
         <v>121408711</v>
       </c>
       <c r="B186" t="n">
-        <v>91683</v>
+        <v>91695</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -6522,7 +6522,7 @@
         <v>112129200</v>
       </c>
       <c r="B51" t="n">
-        <v>90242</v>
+        <v>90243</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>119058657</v>
       </c>
       <c r="B169" t="n">
-        <v>91993</v>
+        <v>91994</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -21549,7 +21549,7 @@
         <v>119130129</v>
       </c>
       <c r="B179" t="n">
-        <v>90237</v>
+        <v>90238</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -22314,7 +22314,7 @@
         <v>121408711</v>
       </c>
       <c r="B186" t="n">
-        <v>91695</v>
+        <v>91696</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -6522,7 +6522,7 @@
         <v>112129200</v>
       </c>
       <c r="B51" t="n">
-        <v>90243</v>
+        <v>90246</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>119058657</v>
       </c>
       <c r="B169" t="n">
-        <v>91994</v>
+        <v>91997</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -21549,7 +21549,7 @@
         <v>119130129</v>
       </c>
       <c r="B179" t="n">
-        <v>90238</v>
+        <v>90241</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -22314,7 +22314,7 @@
         <v>121408711</v>
       </c>
       <c r="B186" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY186"/>
+  <dimension ref="A1:AY187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22415,6 +22415,126 @@
         </is>
       </c>
     </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>112311188</v>
+      </c>
+      <c r="B187" t="n">
+        <v>86311</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>3767</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Violettfläckig spindling</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Cortinarius violaceomaculatus</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>Haggård, Upl</t>
+        </is>
+      </c>
+      <c r="Q187" t="n">
+        <v>705870</v>
+      </c>
+      <c r="R187" t="n">
+        <v>6634789</v>
+      </c>
+      <c r="S187" t="n">
+        <v>5</v>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AD187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF187" t="inlineStr"/>
+      <c r="AG187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT187" t="inlineStr"/>
+      <c r="AW187" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX187" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY187" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -6522,7 +6522,7 @@
         <v>112129200</v>
       </c>
       <c r="B51" t="n">
-        <v>90246</v>
+        <v>90252</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>119058657</v>
       </c>
       <c r="B169" t="n">
-        <v>91997</v>
+        <v>92003</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -21549,7 +21549,7 @@
         <v>119130129</v>
       </c>
       <c r="B179" t="n">
-        <v>90241</v>
+        <v>90247</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -22314,7 +22314,7 @@
         <v>121408711</v>
       </c>
       <c r="B186" t="n">
-        <v>91699</v>
+        <v>91705</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -22417,10 +22417,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>112311188</v>
+        <v>112311160</v>
       </c>
       <c r="B187" t="n">
-        <v>86311</v>
+        <v>86314</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -22495,7 +22495,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -22505,7 +22505,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD187" t="b">

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -6522,7 +6522,7 @@
         <v>112129200</v>
       </c>
       <c r="B51" t="n">
-        <v>90252</v>
+        <v>90253</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -21549,7 +21549,7 @@
         <v>119130129</v>
       </c>
       <c r="B179" t="n">
-        <v>90247</v>
+        <v>90248</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -22314,7 +22314,7 @@
         <v>121408711</v>
       </c>
       <c r="B186" t="n">
-        <v>91705</v>
+        <v>91706</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -22420,7 +22420,7 @@
         <v>112311160</v>
       </c>
       <c r="B187" t="n">
-        <v>86314</v>
+        <v>86315</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -6522,7 +6522,7 @@
         <v>112129200</v>
       </c>
       <c r="B51" t="n">
-        <v>90253</v>
+        <v>90260</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -21549,7 +21549,7 @@
         <v>119130129</v>
       </c>
       <c r="B179" t="n">
-        <v>90248</v>
+        <v>90255</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -22314,7 +22314,7 @@
         <v>121408711</v>
       </c>
       <c r="B186" t="n">
-        <v>91706</v>
+        <v>91714</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -22417,10 +22417,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>112311160</v>
+        <v>112311188</v>
       </c>
       <c r="B187" t="n">
-        <v>86315</v>
+        <v>86322</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -22495,7 +22495,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -22505,7 +22505,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD187" t="b">

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -22417,7 +22417,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>112311188</v>
+        <v>112311160</v>
       </c>
       <c r="B187" t="n">
         <v>86322</v>
@@ -22495,7 +22495,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -22505,7 +22505,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD187" t="b">

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -22417,7 +22417,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>112311160</v>
+        <v>112311188</v>
       </c>
       <c r="B187" t="n">
         <v>86322</v>
@@ -22495,7 +22495,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -22505,7 +22505,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD187" t="b">

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -19840,7 +19840,7 @@
         <v>119058664</v>
       </c>
       <c r="B164" t="n">
-        <v>98091</v>
+        <v>98109</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -19840,7 +19840,7 @@
         <v>119058664</v>
       </c>
       <c r="B164" t="n">
-        <v>98109</v>
+        <v>98111</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -19840,7 +19840,7 @@
         <v>119058664</v>
       </c>
       <c r="B164" t="n">
-        <v>98111</v>
+        <v>98118</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -19840,7 +19840,7 @@
         <v>119058664</v>
       </c>
       <c r="B164" t="n">
-        <v>98118</v>
+        <v>98127</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -19840,7 +19840,7 @@
         <v>119058664</v>
       </c>
       <c r="B164" t="n">
-        <v>98127</v>
+        <v>98135</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -6041,7 +6041,7 @@
         <v>112130595</v>
       </c>
       <c r="B47" t="n">
-        <v>90455</v>
+        <v>90459</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -6041,7 +6041,7 @@
         <v>112130595</v>
       </c>
       <c r="B47" t="n">
-        <v>90459</v>
+        <v>90467</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -6041,7 +6041,7 @@
         <v>112130595</v>
       </c>
       <c r="B47" t="n">
-        <v>90467</v>
+        <v>90470</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -6041,7 +6041,7 @@
         <v>112130595</v>
       </c>
       <c r="B47" t="n">
-        <v>90470</v>
+        <v>90472</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -6041,7 +6041,7 @@
         <v>112130595</v>
       </c>
       <c r="B47" t="n">
-        <v>90472</v>
+        <v>90478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -4705,36 +4705,38 @@
         <v>112129037</v>
       </c>
       <c r="B36" t="n">
-        <v>89481</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90976</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>233193</v>
+        <v>5733</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Såpfingersvamp</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramaria flavoides</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schild, 1981</t>
+          <t>(Vent.) Schild</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Rantet (Rantet), Upl</t>
+          <t>Rantet, Rantet, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
@@ -4797,6 +4799,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -6041,29 +6044,29 @@
         <v>112130595</v>
       </c>
       <c r="B47" t="n">
-        <v>90481</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90976</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>233193</v>
+        <v>5733</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Såpfingersvamp</t>
+        </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramaria flavoides</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schild, 1981</t>
+          <t>(Vent.) Schild</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -11310,36 +11313,38 @@
         <v>112129316</v>
       </c>
       <c r="B91" t="n">
-        <v>89481</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90976</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>233193</v>
+        <v>5733</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Såpfingersvamp</t>
+        </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramaria flavoides</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Schild, 1981</t>
+          <t>(Vent.) Schild</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Rantet (Rantet), Upl</t>
+          <t>Rantet, Rantet, Upl</t>
         </is>
       </c>
       <c r="Q91" t="n">
@@ -11402,6 +11407,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY188"/>
+  <dimension ref="A1:AY189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22656,6 +22656,107 @@
         </is>
       </c>
     </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>128646668</v>
+      </c>
+      <c r="B189" t="n">
+        <v>92761</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>Haggård, Upl</t>
+        </is>
+      </c>
+      <c r="Q189" t="n">
+        <v>706036</v>
+      </c>
+      <c r="R189" t="n">
+        <v>6634675</v>
+      </c>
+      <c r="S189" t="n">
+        <v>10</v>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF189" t="inlineStr"/>
+      <c r="AG189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT189" t="inlineStr"/>
+      <c r="AW189" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AX189" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY189" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -4705,7 +4705,7 @@
         <v>112129037</v>
       </c>
       <c r="B36" t="n">
-        <v>90976</v>
+        <v>90982</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>112130595</v>
       </c>
       <c r="B47" t="n">
-        <v>90976</v>
+        <v>90982</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>112129316</v>
       </c>
       <c r="B91" t="n">
-        <v>90976</v>
+        <v>90982</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         <v>128646668</v>
       </c>
       <c r="B189" t="n">
-        <v>92761</v>
+        <v>92766</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -4705,7 +4705,7 @@
         <v>112129037</v>
       </c>
       <c r="B36" t="n">
-        <v>90982</v>
+        <v>90988</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>112130595</v>
       </c>
       <c r="B47" t="n">
-        <v>90982</v>
+        <v>90988</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>112129316</v>
       </c>
       <c r="B91" t="n">
-        <v>90982</v>
+        <v>90988</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         <v>128646668</v>
       </c>
       <c r="B189" t="n">
-        <v>92766</v>
+        <v>92772</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -4705,7 +4705,7 @@
         <v>112129037</v>
       </c>
       <c r="B36" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>112130595</v>
       </c>
       <c r="B47" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>112129316</v>
       </c>
       <c r="B91" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         <v>128646668</v>
       </c>
       <c r="B189" t="n">
-        <v>92772</v>
+        <v>92774</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY189"/>
+  <dimension ref="A1:AY194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22757,6 +22757,585 @@
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>128795243</v>
+      </c>
+      <c r="B190" t="n">
+        <v>86949</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>449</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>Haggård, Upl</t>
+        </is>
+      </c>
+      <c r="Q190" t="n">
+        <v>706031</v>
+      </c>
+      <c r="R190" t="n">
+        <v>6634722</v>
+      </c>
+      <c r="S190" t="n">
+        <v>10</v>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF190" t="inlineStr"/>
+      <c r="AG190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT190" t="inlineStr"/>
+      <c r="AW190" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AX190" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>128795240</v>
+      </c>
+      <c r="B191" t="n">
+        <v>92764</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>2058</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Koppartaggsvamp</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Hydnellum lundellii</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>Haggård, Upl</t>
+        </is>
+      </c>
+      <c r="Q191" t="n">
+        <v>706031</v>
+      </c>
+      <c r="R191" t="n">
+        <v>6634722</v>
+      </c>
+      <c r="S191" t="n">
+        <v>10</v>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF191" t="inlineStr"/>
+      <c r="AG191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT191" t="inlineStr"/>
+      <c r="AW191" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AX191" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>128795248</v>
+      </c>
+      <c r="B192" t="n">
+        <v>92774</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>Haggård, Upl</t>
+        </is>
+      </c>
+      <c r="Q192" t="n">
+        <v>706018</v>
+      </c>
+      <c r="R192" t="n">
+        <v>6634707</v>
+      </c>
+      <c r="S192" t="n">
+        <v>10</v>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB192" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF192" t="inlineStr"/>
+      <c r="AG192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT192" t="inlineStr"/>
+      <c r="AW192" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AX192" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>128795252</v>
+      </c>
+      <c r="B193" t="n">
+        <v>86828</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>3611</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Kungsspindling</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Cortinarius elegantior</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>Haggård, Upl</t>
+        </is>
+      </c>
+      <c r="Q193" t="n">
+        <v>706019</v>
+      </c>
+      <c r="R193" t="n">
+        <v>6634703</v>
+      </c>
+      <c r="S193" t="n">
+        <v>10</v>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF193" t="inlineStr"/>
+      <c r="AG193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT193" t="inlineStr"/>
+      <c r="AW193" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AX193" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>128795234</v>
+      </c>
+      <c r="B194" t="n">
+        <v>92748</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>Haggård, Upl</t>
+        </is>
+      </c>
+      <c r="Q194" t="n">
+        <v>705995</v>
+      </c>
+      <c r="R194" t="n">
+        <v>6634685</v>
+      </c>
+      <c r="S194" t="n">
+        <v>10</v>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF194" t="inlineStr"/>
+      <c r="AG194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT194" t="inlineStr"/>
+      <c r="AW194" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AX194" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY194" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY194"/>
+  <dimension ref="A1:AY195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4705,7 +4705,7 @@
         <v>112129037</v>
       </c>
       <c r="B36" t="n">
-        <v>90990</v>
+        <v>90991</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>112130595</v>
       </c>
       <c r="B47" t="n">
-        <v>90990</v>
+        <v>90991</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>112129316</v>
       </c>
       <c r="B91" t="n">
-        <v>90990</v>
+        <v>90991</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         <v>128646668</v>
       </c>
       <c r="B189" t="n">
-        <v>92774</v>
+        <v>92775</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22759,10 +22759,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128795243</v>
+        <v>128795240</v>
       </c>
       <c r="B190" t="n">
-        <v>86949</v>
+        <v>92765</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22770,25 +22770,33 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>449</v>
+        <v>2058</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
@@ -22870,10 +22878,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128795240</v>
+        <v>128795243</v>
       </c>
       <c r="B191" t="n">
-        <v>92764</v>
+        <v>86949</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22881,33 +22889,25 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>2058</v>
+        <v>449</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr"/>
       <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
@@ -22992,7 +22992,7 @@
         <v>128795248</v>
       </c>
       <c r="B192" t="n">
-        <v>92774</v>
+        <v>92775</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>128795234</v>
       </c>
       <c r="B194" t="n">
-        <v>92748</v>
+        <v>92749</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23335,6 +23335,115 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>128811184</v>
+      </c>
+      <c r="B195" t="n">
+        <v>90227</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>1593</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Lakritsmusseron</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Tricholoma apium</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Jul.Schäff.</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>Haggård, Upl</t>
+        </is>
+      </c>
+      <c r="Q195" t="n">
+        <v>706019</v>
+      </c>
+      <c r="R195" t="n">
+        <v>6634703</v>
+      </c>
+      <c r="S195" t="n">
+        <v>10</v>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF195" t="inlineStr"/>
+      <c r="AG195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT195" t="inlineStr"/>
+      <c r="AW195" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AX195" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY195" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -4705,7 +4705,7 @@
         <v>112129037</v>
       </c>
       <c r="B36" t="n">
-        <v>90991</v>
+        <v>91018</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>112130595</v>
       </c>
       <c r="B47" t="n">
-        <v>90991</v>
+        <v>91018</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>112129316</v>
       </c>
       <c r="B91" t="n">
-        <v>90991</v>
+        <v>91018</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         <v>128646668</v>
       </c>
       <c r="B189" t="n">
-        <v>92775</v>
+        <v>92802</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22759,10 +22759,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128795240</v>
+        <v>128795243</v>
       </c>
       <c r="B190" t="n">
-        <v>92765</v>
+        <v>86976</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22770,33 +22770,25 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>2058</v>
+        <v>449</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
@@ -22878,10 +22870,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128795243</v>
+        <v>128795240</v>
       </c>
       <c r="B191" t="n">
-        <v>86949</v>
+        <v>92792</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22889,25 +22881,33 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>449</v>
+        <v>2058</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K191" t="inlineStr"/>
       <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
@@ -22992,7 +22992,7 @@
         <v>128795248</v>
       </c>
       <c r="B192" t="n">
-        <v>92775</v>
+        <v>92802</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>128795252</v>
       </c>
       <c r="B193" t="n">
-        <v>86828</v>
+        <v>86855</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>128795234</v>
       </c>
       <c r="B194" t="n">
-        <v>92749</v>
+        <v>92776</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>128811184</v>
       </c>
       <c r="B195" t="n">
-        <v>90227</v>
+        <v>90254</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -4705,7 +4705,7 @@
         <v>112129037</v>
       </c>
       <c r="B36" t="n">
-        <v>91018</v>
+        <v>91023</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>112130595</v>
       </c>
       <c r="B47" t="n">
-        <v>91018</v>
+        <v>91023</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>112129316</v>
       </c>
       <c r="B91" t="n">
-        <v>91018</v>
+        <v>91023</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         <v>128646668</v>
       </c>
       <c r="B189" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22759,10 +22759,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128795243</v>
+        <v>128795240</v>
       </c>
       <c r="B190" t="n">
-        <v>86976</v>
+        <v>92797</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22770,25 +22770,33 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>449</v>
+        <v>2058</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
@@ -22870,10 +22878,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128795240</v>
+        <v>128795243</v>
       </c>
       <c r="B191" t="n">
-        <v>92792</v>
+        <v>86980</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22881,33 +22889,25 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>2058</v>
+        <v>449</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr"/>
       <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
@@ -22992,7 +22992,7 @@
         <v>128795248</v>
       </c>
       <c r="B192" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>128795252</v>
       </c>
       <c r="B193" t="n">
-        <v>86855</v>
+        <v>86859</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>128795234</v>
       </c>
       <c r="B194" t="n">
-        <v>92776</v>
+        <v>92781</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>128811184</v>
       </c>
       <c r="B195" t="n">
-        <v>90254</v>
+        <v>90259</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -4705,7 +4705,7 @@
         <v>112129037</v>
       </c>
       <c r="B36" t="n">
-        <v>91023</v>
+        <v>91028</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>112130595</v>
       </c>
       <c r="B47" t="n">
-        <v>91023</v>
+        <v>91028</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>112129316</v>
       </c>
       <c r="B91" t="n">
-        <v>91023</v>
+        <v>91028</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         <v>128646668</v>
       </c>
       <c r="B189" t="n">
-        <v>92807</v>
+        <v>92812</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22759,10 +22759,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128795240</v>
+        <v>128795243</v>
       </c>
       <c r="B190" t="n">
-        <v>92797</v>
+        <v>86981</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22770,33 +22770,25 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>2058</v>
+        <v>449</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
@@ -22878,10 +22870,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128795243</v>
+        <v>128795240</v>
       </c>
       <c r="B191" t="n">
-        <v>86980</v>
+        <v>92802</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22889,25 +22881,33 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>449</v>
+        <v>2058</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K191" t="inlineStr"/>
       <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
@@ -22992,7 +22992,7 @@
         <v>128795248</v>
       </c>
       <c r="B192" t="n">
-        <v>92807</v>
+        <v>92812</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>128795252</v>
       </c>
       <c r="B193" t="n">
-        <v>86859</v>
+        <v>86860</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>128795234</v>
       </c>
       <c r="B194" t="n">
-        <v>92781</v>
+        <v>92786</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>128811184</v>
       </c>
       <c r="B195" t="n">
-        <v>90259</v>
+        <v>90264</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY195"/>
+  <dimension ref="A1:AY197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23445,6 +23445,241 @@
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>128924622</v>
+      </c>
+      <c r="B196" t="n">
+        <v>92830</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>Rantet 500-600 m V-SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q196" t="n">
+        <v>705949</v>
+      </c>
+      <c r="R196" t="n">
+        <v>6634881</v>
+      </c>
+      <c r="S196" t="n">
+        <v>5</v>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>2023-09-16</t>
+        </is>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>2023-09-16</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="AD196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF196" t="inlineStr"/>
+      <c r="AG196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI196" t="inlineStr">
+        <is>
+          <t>Kalkpåverkad luckig granskog, mossrik</t>
+        </is>
+      </c>
+      <c r="AT196" t="inlineStr"/>
+      <c r="AW196" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX196" t="inlineStr">
+        <is>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>128924620</v>
+      </c>
+      <c r="B197" t="n">
+        <v>91013</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>Rantet 500-600 m V-SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q197" t="n">
+        <v>705949</v>
+      </c>
+      <c r="R197" t="n">
+        <v>6634881</v>
+      </c>
+      <c r="S197" t="n">
+        <v>5</v>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>2023-09-16</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>2023-09-16</t>
+        </is>
+      </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="AD197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>Kalkpåverkad luckig granskog, mossrik</t>
+        </is>
+      </c>
+      <c r="AT197" t="inlineStr"/>
+      <c r="AW197" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX197" t="inlineStr">
+        <is>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY197" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -4705,7 +4705,7 @@
         <v>112129037</v>
       </c>
       <c r="B36" t="n">
-        <v>91028</v>
+        <v>91032</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>112130595</v>
       </c>
       <c r="B47" t="n">
-        <v>91028</v>
+        <v>91032</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>112129316</v>
       </c>
       <c r="B91" t="n">
-        <v>91028</v>
+        <v>91032</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         <v>128646668</v>
       </c>
       <c r="B189" t="n">
-        <v>92812</v>
+        <v>92816</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>128795243</v>
       </c>
       <c r="B190" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>128795240</v>
       </c>
       <c r="B191" t="n">
-        <v>92802</v>
+        <v>92806</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>128795248</v>
       </c>
       <c r="B192" t="n">
-        <v>92812</v>
+        <v>92816</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>128795252</v>
       </c>
       <c r="B193" t="n">
-        <v>86860</v>
+        <v>86864</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>128795234</v>
       </c>
       <c r="B194" t="n">
-        <v>92786</v>
+        <v>92790</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>128811184</v>
       </c>
       <c r="B195" t="n">
-        <v>90264</v>
+        <v>90268</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>128924622</v>
       </c>
       <c r="B196" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>128924620</v>
       </c>
       <c r="B197" t="n">
-        <v>91013</v>
+        <v>91017</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -22759,10 +22759,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128795243</v>
+        <v>128795240</v>
       </c>
       <c r="B190" t="n">
-        <v>86985</v>
+        <v>92806</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22770,25 +22770,33 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>449</v>
+        <v>2058</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
@@ -22870,10 +22878,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128795240</v>
+        <v>128795243</v>
       </c>
       <c r="B191" t="n">
-        <v>92806</v>
+        <v>86985</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22881,33 +22889,25 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>2058</v>
+        <v>449</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr"/>
       <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -22759,10 +22759,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128795240</v>
+        <v>128795243</v>
       </c>
       <c r="B190" t="n">
-        <v>92806</v>
+        <v>86985</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22770,33 +22770,25 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>2058</v>
+        <v>449</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
@@ -22878,10 +22870,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128795243</v>
+        <v>128795240</v>
       </c>
       <c r="B191" t="n">
-        <v>86985</v>
+        <v>92806</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22889,25 +22881,33 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>449</v>
+        <v>2058</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K191" t="inlineStr"/>
       <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -4705,7 +4705,7 @@
         <v>112129037</v>
       </c>
       <c r="B36" t="n">
-        <v>91032</v>
+        <v>91037</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>112130595</v>
       </c>
       <c r="B47" t="n">
-        <v>91032</v>
+        <v>91037</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>112129316</v>
       </c>
       <c r="B91" t="n">
-        <v>91032</v>
+        <v>91037</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         <v>128646668</v>
       </c>
       <c r="B189" t="n">
-        <v>92816</v>
+        <v>92821</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22759,10 +22759,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128795243</v>
+        <v>128795240</v>
       </c>
       <c r="B190" t="n">
-        <v>86985</v>
+        <v>92811</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22770,25 +22770,33 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>449</v>
+        <v>2058</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
@@ -22870,10 +22878,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128795240</v>
+        <v>128795243</v>
       </c>
       <c r="B191" t="n">
-        <v>92806</v>
+        <v>86990</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22881,33 +22889,25 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>2058</v>
+        <v>449</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr"/>
       <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
@@ -22992,7 +22992,7 @@
         <v>128795248</v>
       </c>
       <c r="B192" t="n">
-        <v>92816</v>
+        <v>92821</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>128795252</v>
       </c>
       <c r="B193" t="n">
-        <v>86864</v>
+        <v>86869</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>128795234</v>
       </c>
       <c r="B194" t="n">
-        <v>92790</v>
+        <v>92795</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>128811184</v>
       </c>
       <c r="B195" t="n">
-        <v>90268</v>
+        <v>90273</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>128924622</v>
       </c>
       <c r="B196" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>128924620</v>
       </c>
       <c r="B197" t="n">
-        <v>91017</v>
+        <v>91022</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -4705,7 +4705,7 @@
         <v>112129037</v>
       </c>
       <c r="B36" t="n">
-        <v>91039</v>
+        <v>91044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>112130595</v>
       </c>
       <c r="B47" t="n">
-        <v>91039</v>
+        <v>91044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>112129316</v>
       </c>
       <c r="B91" t="n">
-        <v>91039</v>
+        <v>91044</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         <v>128646668</v>
       </c>
       <c r="B189" t="n">
-        <v>92824</v>
+        <v>92829</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22759,10 +22759,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128795243</v>
+        <v>128795240</v>
       </c>
       <c r="B190" t="n">
-        <v>86997</v>
+        <v>92819</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22770,25 +22770,33 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>449</v>
+        <v>2058</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
@@ -22870,10 +22878,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128795240</v>
+        <v>128795243</v>
       </c>
       <c r="B191" t="n">
-        <v>92819</v>
+        <v>86997</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22881,33 +22889,25 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>2058</v>
+        <v>449</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr"/>
       <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -22762,7 +22762,7 @@
         <v>128795240</v>
       </c>
       <c r="B190" t="n">
-        <v>92819</v>
+        <v>92824</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>128795243</v>
       </c>
       <c r="B191" t="n">
-        <v>86997</v>
+        <v>87000</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>128795248</v>
       </c>
       <c r="B192" t="n">
-        <v>92829</v>
+        <v>92834</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>128795252</v>
       </c>
       <c r="B193" t="n">
-        <v>86876</v>
+        <v>86879</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>128795234</v>
       </c>
       <c r="B194" t="n">
-        <v>92803</v>
+        <v>92808</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>128811184</v>
       </c>
       <c r="B195" t="n">
-        <v>90280</v>
+        <v>90283</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>128924622</v>
       </c>
       <c r="B196" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>128924620</v>
       </c>
       <c r="B197" t="n">
-        <v>91029</v>
+        <v>91032</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -4705,7 +4705,7 @@
         <v>112129037</v>
       </c>
       <c r="B36" t="n">
-        <v>91044</v>
+        <v>91050</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>112130595</v>
       </c>
       <c r="B47" t="n">
-        <v>91044</v>
+        <v>91050</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>112129316</v>
       </c>
       <c r="B91" t="n">
-        <v>91044</v>
+        <v>91050</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         <v>128646668</v>
       </c>
       <c r="B189" t="n">
-        <v>92829</v>
+        <v>92837</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22759,10 +22759,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128795240</v>
+        <v>128795243</v>
       </c>
       <c r="B190" t="n">
-        <v>92824</v>
+        <v>87003</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22770,33 +22770,25 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>2058</v>
+        <v>449</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
@@ -22878,10 +22870,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128795243</v>
+        <v>128795240</v>
       </c>
       <c r="B191" t="n">
-        <v>87000</v>
+        <v>92827</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22889,25 +22881,33 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>449</v>
+        <v>2058</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K191" t="inlineStr"/>
       <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
@@ -22992,7 +22992,7 @@
         <v>128795248</v>
       </c>
       <c r="B192" t="n">
-        <v>92834</v>
+        <v>92837</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>128795252</v>
       </c>
       <c r="B193" t="n">
-        <v>86879</v>
+        <v>86882</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>128795234</v>
       </c>
       <c r="B194" t="n">
-        <v>92808</v>
+        <v>92811</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>128811184</v>
       </c>
       <c r="B195" t="n">
-        <v>90283</v>
+        <v>90286</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>128924622</v>
       </c>
       <c r="B196" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>128924620</v>
       </c>
       <c r="B197" t="n">
-        <v>91032</v>
+        <v>91035</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -22661,7 +22661,7 @@
         <v>128646668</v>
       </c>
       <c r="B189" t="n">
-        <v>92837</v>
+        <v>92844</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22759,10 +22759,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128795243</v>
+        <v>128795240</v>
       </c>
       <c r="B190" t="n">
-        <v>87003</v>
+        <v>92834</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22770,25 +22770,33 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>449</v>
+        <v>2058</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
@@ -22870,10 +22878,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128795240</v>
+        <v>128795243</v>
       </c>
       <c r="B191" t="n">
-        <v>92827</v>
+        <v>87007</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22881,33 +22889,25 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>2058</v>
+        <v>449</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr"/>
       <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
@@ -22992,7 +22992,7 @@
         <v>128795248</v>
       </c>
       <c r="B192" t="n">
-        <v>92837</v>
+        <v>92844</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>128795252</v>
       </c>
       <c r="B193" t="n">
-        <v>86882</v>
+        <v>86886</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>128795234</v>
       </c>
       <c r="B194" t="n">
-        <v>92811</v>
+        <v>92818</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>128811184</v>
       </c>
       <c r="B195" t="n">
-        <v>90286</v>
+        <v>90290</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>128924622</v>
       </c>
       <c r="B196" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>128924620</v>
       </c>
       <c r="B197" t="n">
-        <v>91035</v>
+        <v>91039</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -22759,10 +22759,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128795240</v>
+        <v>128795243</v>
       </c>
       <c r="B190" t="n">
-        <v>92834</v>
+        <v>87014</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22770,33 +22770,25 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>2058</v>
+        <v>449</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
@@ -22878,10 +22870,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128795243</v>
+        <v>128795240</v>
       </c>
       <c r="B191" t="n">
-        <v>87007</v>
+        <v>92841</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22889,25 +22881,33 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>449</v>
+        <v>2058</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K191" t="inlineStr"/>
       <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
@@ -22992,7 +22992,7 @@
         <v>128795248</v>
       </c>
       <c r="B192" t="n">
-        <v>92844</v>
+        <v>92851</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>128795252</v>
       </c>
       <c r="B193" t="n">
-        <v>86886</v>
+        <v>86893</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>128795234</v>
       </c>
       <c r="B194" t="n">
-        <v>92818</v>
+        <v>92825</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>128811184</v>
       </c>
       <c r="B195" t="n">
-        <v>90290</v>
+        <v>90297</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>128924622</v>
       </c>
       <c r="B196" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>128924620</v>
       </c>
       <c r="B197" t="n">
-        <v>91039</v>
+        <v>91046</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -22759,10 +22759,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128795243</v>
+        <v>128795240</v>
       </c>
       <c r="B190" t="n">
-        <v>87014</v>
+        <v>92843</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22770,25 +22770,33 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>449</v>
+        <v>2058</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
@@ -22870,10 +22878,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128795240</v>
+        <v>128795243</v>
       </c>
       <c r="B191" t="n">
-        <v>92841</v>
+        <v>87016</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22881,33 +22889,25 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>2058</v>
+        <v>449</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr"/>
       <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
@@ -22992,7 +22992,7 @@
         <v>128795248</v>
       </c>
       <c r="B192" t="n">
-        <v>92851</v>
+        <v>92853</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>128795252</v>
       </c>
       <c r="B193" t="n">
-        <v>86893</v>
+        <v>86895</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>128795234</v>
       </c>
       <c r="B194" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>128811184</v>
       </c>
       <c r="B195" t="n">
-        <v>90297</v>
+        <v>90299</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>128924622</v>
       </c>
       <c r="B196" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>128924620</v>
       </c>
       <c r="B197" t="n">
-        <v>91046</v>
+        <v>91048</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -22759,10 +22759,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128795240</v>
+        <v>128795243</v>
       </c>
       <c r="B190" t="n">
-        <v>92843</v>
+        <v>87016</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22770,33 +22770,25 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>2058</v>
+        <v>449</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
@@ -22878,10 +22870,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128795243</v>
+        <v>128795240</v>
       </c>
       <c r="B191" t="n">
-        <v>87016</v>
+        <v>92843</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22889,25 +22881,33 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>449</v>
+        <v>2058</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K191" t="inlineStr"/>
       <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -22759,10 +22759,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128795243</v>
+        <v>128795240</v>
       </c>
       <c r="B190" t="n">
-        <v>87016</v>
+        <v>92829</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22770,25 +22770,33 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>449</v>
+        <v>2058</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
@@ -22870,10 +22878,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128795240</v>
+        <v>128795243</v>
       </c>
       <c r="B191" t="n">
-        <v>92843</v>
+        <v>87017</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22881,33 +22889,25 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>2058</v>
+        <v>449</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr"/>
       <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
@@ -22992,7 +22992,7 @@
         <v>128795248</v>
       </c>
       <c r="B192" t="n">
-        <v>92853</v>
+        <v>92839</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>128795252</v>
       </c>
       <c r="B193" t="n">
-        <v>86895</v>
+        <v>86896</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>128795234</v>
       </c>
       <c r="B194" t="n">
-        <v>92827</v>
+        <v>92813</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>128811184</v>
       </c>
       <c r="B195" t="n">
-        <v>90299</v>
+        <v>90300</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>128924622</v>
       </c>
       <c r="B196" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>128924620</v>
       </c>
       <c r="B197" t="n">
-        <v>91048</v>
+        <v>91049</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -23450,7 +23450,7 @@
         <v>128924622</v>
       </c>
       <c r="B196" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23558,7 +23558,7 @@
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Viktor Lund, Martin Axegård, Joakim Ekman</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
@@ -23675,7 +23675,7 @@
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
+          <t>Viktor Lund, Martin Axegård, Joakim Ekman</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -23558,7 +23558,7 @@
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård, Joakim Ekman</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
@@ -23675,7 +23675,7 @@
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård, Joakim Ekman</t>
+          <t>Joakim Ekman, Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -23450,7 +23450,7 @@
         <v>128924622</v>
       </c>
       <c r="B196" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>128924620</v>
       </c>
       <c r="B197" t="n">
-        <v>91049</v>
+        <v>91052</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -23450,7 +23450,7 @@
         <v>128924622</v>
       </c>
       <c r="B196" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>128924620</v>
       </c>
       <c r="B197" t="n">
-        <v>91052</v>
+        <v>91054</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -23450,7 +23450,7 @@
         <v>128924622</v>
       </c>
       <c r="B196" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>128924620</v>
       </c>
       <c r="B197" t="n">
-        <v>91054</v>
+        <v>91058</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -4797,7 +4797,7 @@
         <v>0</v>
       </c>
       <c r="AE36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
@@ -6131,7 +6131,7 @@
         <v>0</v>
       </c>
       <c r="AE47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
@@ -7332,7 +7332,7 @@
         <v>0</v>
       </c>
       <c r="AE57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG57" t="b">
         <v>0</v>
@@ -8913,7 +8913,7 @@
         <v>0</v>
       </c>
       <c r="AE70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG70" t="b">
         <v>0</v>
@@ -11405,7 +11405,7 @@
         <v>0</v>
       </c>
       <c r="AE91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
@@ -20529,7 +20529,7 @@
         <v>0</v>
       </c>
       <c r="AE169" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG169" t="b">
         <v>0</v>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY197"/>
+  <dimension ref="A1:AY201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23680,6 +23680,410 @@
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>131431255</v>
+      </c>
+      <c r="B198" t="n">
+        <v>91343</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>Haggård, Upl</t>
+        </is>
+      </c>
+      <c r="Q198" t="n">
+        <v>705999</v>
+      </c>
+      <c r="R198" t="n">
+        <v>6634781</v>
+      </c>
+      <c r="S198" t="n">
+        <v>10</v>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT198" t="inlineStr"/>
+      <c r="AW198" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX198" t="inlineStr">
+        <is>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AY198" t="inlineStr">
+        <is>
+          <t>Värdefull natur i Stockholms län</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>131431258</v>
+      </c>
+      <c r="B199" t="n">
+        <v>93100</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>4363</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Hydnellum concrescens</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>Haggård, Upl</t>
+        </is>
+      </c>
+      <c r="Q199" t="n">
+        <v>705968</v>
+      </c>
+      <c r="R199" t="n">
+        <v>6634619</v>
+      </c>
+      <c r="S199" t="n">
+        <v>10</v>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT199" t="inlineStr"/>
+      <c r="AW199" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX199" t="inlineStr">
+        <is>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AY199" t="inlineStr">
+        <is>
+          <t>Värdefull natur i Stockholms län</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>131431257</v>
+      </c>
+      <c r="B200" t="n">
+        <v>93093</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>150</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Grangråticka</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Boletopsis leucomelaena</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>Haggård, Upl</t>
+        </is>
+      </c>
+      <c r="Q200" t="n">
+        <v>705973</v>
+      </c>
+      <c r="R200" t="n">
+        <v>6634708</v>
+      </c>
+      <c r="S200" t="n">
+        <v>10</v>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT200" t="inlineStr"/>
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX200" t="inlineStr">
+        <is>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AY200" t="inlineStr">
+        <is>
+          <t>Värdefull natur i Stockholms län</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>131431256</v>
+      </c>
+      <c r="B201" t="n">
+        <v>91283</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>720</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Violgubbe</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Gomphus clavatus</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>Haggård, Upl</t>
+        </is>
+      </c>
+      <c r="Q201" t="n">
+        <v>705949</v>
+      </c>
+      <c r="R201" t="n">
+        <v>6634721</v>
+      </c>
+      <c r="S201" t="n">
+        <v>10</v>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT201" t="inlineStr"/>
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX201" t="inlineStr">
+        <is>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AY201" t="inlineStr">
+        <is>
+          <t>Värdefull natur i Stockholms län</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -23685,7 +23685,7 @@
         <v>131431255</v>
       </c>
       <c r="B198" t="n">
-        <v>91348</v>
+        <v>91354</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23786,7 +23786,7 @@
         <v>131431258</v>
       </c>
       <c r="B199" t="n">
-        <v>93105</v>
+        <v>93111</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23887,7 +23887,7 @@
         <v>131431257</v>
       </c>
       <c r="B200" t="n">
-        <v>93098</v>
+        <v>93104</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>131431256</v>
       </c>
       <c r="B201" t="n">
-        <v>91288</v>
+        <v>91294</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -20788,12 +20788,7 @@
         <v>119058610</v>
       </c>
       <c r="B172" t="n">
-        <v>90073</v>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91347</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -23781,7 +23781,7 @@
         <v>131431258</v>
       </c>
       <c r="B199" t="n">
-        <v>93111</v>
+        <v>93112</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23882,7 +23882,7 @@
         <v>131431257</v>
       </c>
       <c r="B200" t="n">
-        <v>93104</v>
+        <v>93105</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -20788,7 +20788,7 @@
         <v>119058610</v>
       </c>
       <c r="B172" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>131431255</v>
       </c>
       <c r="B198" t="n">
-        <v>91354</v>
+        <v>91355</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23781,7 +23781,7 @@
         <v>131431258</v>
       </c>
       <c r="B199" t="n">
-        <v>93112</v>
+        <v>93113</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23882,7 +23882,7 @@
         <v>131431257</v>
       </c>
       <c r="B200" t="n">
-        <v>93105</v>
+        <v>93106</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
         <v>131431256</v>
       </c>
       <c r="B201" t="n">
-        <v>91294</v>
+        <v>91295</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -20788,7 +20788,7 @@
         <v>119058610</v>
       </c>
       <c r="B172" t="n">
-        <v>91348</v>
+        <v>91351</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>131431255</v>
       </c>
       <c r="B198" t="n">
-        <v>91355</v>
+        <v>91358</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23781,7 +23781,7 @@
         <v>131431258</v>
       </c>
       <c r="B199" t="n">
-        <v>93113</v>
+        <v>93116</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23882,7 +23882,7 @@
         <v>131431257</v>
       </c>
       <c r="B200" t="n">
-        <v>93106</v>
+        <v>93109</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
         <v>131431256</v>
       </c>
       <c r="B201" t="n">
-        <v>91295</v>
+        <v>91298</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -20788,7 +20788,7 @@
         <v>119058610</v>
       </c>
       <c r="B172" t="n">
-        <v>91351</v>
+        <v>91357</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>131431255</v>
       </c>
       <c r="B198" t="n">
-        <v>91358</v>
+        <v>91364</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23781,7 +23781,7 @@
         <v>131431258</v>
       </c>
       <c r="B199" t="n">
-        <v>93116</v>
+        <v>93122</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23882,7 +23882,7 @@
         <v>131431257</v>
       </c>
       <c r="B200" t="n">
-        <v>93109</v>
+        <v>93115</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
         <v>131431256</v>
       </c>
       <c r="B201" t="n">
-        <v>91298</v>
+        <v>91304</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -20788,7 +20788,7 @@
         <v>119058610</v>
       </c>
       <c r="B172" t="n">
-        <v>91357</v>
+        <v>91360</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>131431255</v>
       </c>
       <c r="B198" t="n">
-        <v>91364</v>
+        <v>91367</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23781,7 +23781,7 @@
         <v>131431258</v>
       </c>
       <c r="B199" t="n">
-        <v>93122</v>
+        <v>93125</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23882,7 +23882,7 @@
         <v>131431257</v>
       </c>
       <c r="B200" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
         <v>131431256</v>
       </c>
       <c r="B201" t="n">
-        <v>91304</v>
+        <v>91307</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -20788,7 +20788,7 @@
         <v>119058610</v>
       </c>
       <c r="B172" t="n">
-        <v>91360</v>
+        <v>91365</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>131431255</v>
       </c>
       <c r="B198" t="n">
-        <v>91367</v>
+        <v>91372</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23781,7 +23781,7 @@
         <v>131431258</v>
       </c>
       <c r="B199" t="n">
-        <v>93125</v>
+        <v>93130</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23882,7 +23882,7 @@
         <v>131431257</v>
       </c>
       <c r="B200" t="n">
-        <v>93118</v>
+        <v>93123</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
         <v>131431256</v>
       </c>
       <c r="B201" t="n">
-        <v>91307</v>
+        <v>91312</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -20788,7 +20788,7 @@
         <v>119058610</v>
       </c>
       <c r="B172" t="n">
-        <v>91365</v>
+        <v>91367</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -20788,7 +20788,7 @@
         <v>119058610</v>
       </c>
       <c r="B172" t="n">
-        <v>91408</v>
+        <v>91411</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>

--- a/artfynd/A 34045-2023 artfynd.xlsx
+++ b/artfynd/A 34045-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY208"/>
+  <dimension ref="A1:AZ208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112130235</t>
         </is>
       </c>
     </row>
@@ -889,6 +899,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112212357</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128795275</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1109,6 +1129,11 @@
           <t>Värdefull natur i Stockholms län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131431257</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1205,6 +1230,11 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112310654</t>
         </is>
       </c>
     </row>
@@ -1318,6 +1348,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128795243</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1423,6 +1458,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112211995</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1534,6 +1574,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108291348</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1648,6 +1693,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112205486</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1758,6 +1808,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112212091</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1868,6 +1923,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119058634</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1973,6 +2033,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119063626</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2099,6 +2164,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112157770</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2233,6 +2303,11 @@
       <c r="AY15" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112157774</t>
         </is>
       </c>
     </row>
@@ -2340,6 +2415,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112212360</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2445,6 +2525,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112212372</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2557,6 +2642,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112313829</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2658,6 +2748,11 @@
           <t>Värdefull natur i Stockholms län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131431256</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2773,6 +2868,11 @@
       <c r="AY20" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112320037</t>
         </is>
       </c>
     </row>
@@ -2880,6 +2980,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112212050</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2990,6 +3095,11 @@
       <c r="AY22" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112319539</t>
         </is>
       </c>
     </row>
@@ -3127,6 +3237,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112130941</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3235,6 +3350,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108291322</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3345,6 +3465,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112212097</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3453,6 +3578,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113430486</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3563,6 +3693,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119058628</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3673,6 +3808,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119058629</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3814,6 +3954,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112157773</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3953,6 +4098,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112157791</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4065,6 +4215,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112258061</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4172,6 +4327,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115494627</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4284,6 +4444,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112129955</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4398,6 +4563,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112212225</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4510,6 +4680,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112443737</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4617,6 +4792,11 @@
       <c r="AY36" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112212352</t>
         </is>
       </c>
     </row>
@@ -4734,6 +4914,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112257092</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4843,6 +5028,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128811184</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4953,6 +5143,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119058651</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5058,6 +5253,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119063562</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5163,6 +5363,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119063650</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5278,6 +5483,11 @@
       <c r="AY42" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112130162</t>
         </is>
       </c>
     </row>
@@ -5385,6 +5595,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112212238</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5506,6 +5721,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112157762</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5625,6 +5845,11 @@
       <c r="AY45" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112157801</t>
         </is>
       </c>
     </row>
@@ -5732,6 +5957,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112212315</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5837,6 +6067,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112212343</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5945,6 +6180,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112256851</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6053,6 +6293,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112257145</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6163,6 +6408,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119058657</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6268,6 +6518,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119063488</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6387,6 +6642,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128795240</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6499,6 +6759,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112129120</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6611,6 +6876,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112129914</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6732,6 +7002,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112157787</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6844,6 +7119,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112308853</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6965,6 +7245,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113158018</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7077,6 +7362,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112257241</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7198,6 +7488,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113158014</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7337,6 +7632,11 @@
       <c r="AY60" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112157765</t>
         </is>
       </c>
     </row>
@@ -7444,6 +7744,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112211954</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7573,6 +7878,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112157776</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7685,6 +7995,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112257263</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7804,6 +8119,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128795252</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7925,6 +8245,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112157777</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8046,6 +8371,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112157793</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8165,6 +8495,11 @@
       <c r="AY67" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112157799</t>
         </is>
       </c>
     </row>
@@ -8272,6 +8607,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112211976</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8384,6 +8724,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112257509</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8496,6 +8841,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112309070</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8606,6 +8956,11 @@
       <c r="AY71" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112309411</t>
         </is>
       </c>
     </row>
@@ -8713,6 +9068,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112211999</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8825,6 +9185,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112257311</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8937,6 +9302,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112309206</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9049,6 +9419,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112309475</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9151,6 +9526,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112310429</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9253,6 +9633,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112313926</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9355,6 +9740,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112314048</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9469,6 +9859,11 @@
       <c r="AY79" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112493455</t>
         </is>
       </c>
     </row>
@@ -9572,6 +9967,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120521492</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9673,6 +10073,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120521829</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9778,6 +10183,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112215302</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9893,6 +10303,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112311160</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10008,6 +10423,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112130636</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10129,6 +10549,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112157760</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10250,6 +10675,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112157764</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10371,6 +10801,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112157768</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10492,6 +10927,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112157769</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10611,6 +11051,11 @@
       <c r="AY89" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112157775</t>
         </is>
       </c>
     </row>
@@ -10718,6 +11163,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112211957</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10823,6 +11273,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112212028</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10928,6 +11383,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112212058</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11033,6 +11493,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112212332</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11135,6 +11600,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112309877</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11237,6 +11707,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112313201</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11339,6 +11814,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112313523</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11441,6 +11921,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112314024</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11560,6 +12045,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128795234</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11670,6 +12160,11 @@
       <c r="AY99" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112129154</t>
         </is>
       </c>
     </row>
@@ -11787,6 +12282,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119058652</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11892,6 +12392,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119063544</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11993,6 +12498,11 @@
           <t>Värdefull natur i Stockholms län</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131431258</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12105,6 +12615,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112129163</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12215,6 +12730,11 @@
       <c r="AY104" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112130100</t>
         </is>
       </c>
     </row>
@@ -12322,6 +12842,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112212291</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12422,6 +12947,11 @@
       <c r="AY106" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112313173</t>
         </is>
       </c>
     </row>
@@ -12534,6 +13064,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119058659</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12644,6 +13179,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119058662</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12749,6 +13289,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119063646</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12850,6 +13395,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120521723</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12955,6 +13505,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112212376</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13069,6 +13624,11 @@
       <c r="AY112" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112493456</t>
         </is>
       </c>
     </row>
@@ -13172,6 +13732,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646668</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13283,6 +13848,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128795248</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13395,6 +13965,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112314725</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13507,6 +14082,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112129084</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13628,6 +14208,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112157788</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13749,6 +14334,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112157792</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13861,6 +14451,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112256783</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13971,6 +14566,11 @@
       <c r="AY120" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112309124</t>
         </is>
       </c>
     </row>
@@ -14074,6 +14674,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120521743</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14181,6 +14786,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115492384</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14301,6 +14911,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112129037</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14421,6 +15036,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112129316</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14536,6 +15156,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112130595</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14656,6 +15281,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112310414</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14776,6 +15406,11 @@
           <t>Svampar i Roslagen, Fynd med DNA-sekvens - extern</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112315113</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14896,6 +15531,11 @@
           <t>Svampar i Roslagen, Fynd med DNA-sekvens - extern</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118338779</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15016,6 +15656,11 @@
           <t>Svampar i Roslagen, Fynd med DNA-sekvens - extern</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118338782</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15136,6 +15781,11 @@
           <t>Svampar i Roslagen, Fynd med DNA-sekvens - extern</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118815308</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15246,6 +15896,11 @@
           <t>Svampar i Roslagen, Fynd med DNA-sekvens - extern</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120295821</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15358,6 +16013,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112129897</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15479,6 +16139,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112157800</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15598,6 +16263,11 @@
       <c r="AY134" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112157802</t>
         </is>
       </c>
     </row>
@@ -15705,6 +16375,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112212020</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15817,6 +16492,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112257213</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15929,6 +16609,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112309361</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -16031,6 +16716,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112309911</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16133,6 +16823,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112312127</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16234,6 +16929,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120488567</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16351,6 +17051,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128924620</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16472,6 +17177,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112157779</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16591,6 +17301,11 @@
       <c r="AY143" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112157781</t>
         </is>
       </c>
     </row>
@@ -16698,6 +17413,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112212003</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16810,6 +17530,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112128743</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16922,6 +17647,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112128795</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -17034,6 +17764,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112128829</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17161,6 +17896,11 @@
       <c r="AY148" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112157795</t>
         </is>
       </c>
     </row>
@@ -17268,6 +18008,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112212023</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17373,6 +18118,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112212039</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17478,6 +18228,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112212264</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17583,6 +18338,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112212324</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17703,6 +18463,11 @@
           <t>Svampar i Roslagen, Fynd med DNA-sekvens - extern</t>
         </is>
       </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112309002</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17829,6 +18594,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113158012</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17955,6 +18725,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113158013</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -18079,6 +18854,11 @@
       <c r="AY156" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113172635</t>
         </is>
       </c>
     </row>
@@ -18201,6 +18981,11 @@
           <t>Svampar i Roslagen, Fynd med DNA-sekvens - extern</t>
         </is>
       </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118338786</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18321,6 +19106,11 @@
           <t>Svampar i Roslagen, Fynd med DNA-sekvens - extern</t>
         </is>
       </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118815166</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18436,6 +19226,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119058611</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18537,6 +19332,11 @@
           <t>Värdefull natur i Stockholms län</t>
         </is>
       </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131431255</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18649,6 +19449,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112128790</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18768,6 +19573,11 @@
       <c r="AY162" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112157803</t>
         </is>
       </c>
     </row>
@@ -18875,6 +19685,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112212276</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18980,6 +19795,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112212358</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -19101,6 +19921,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113158011</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -19213,6 +20038,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112257802</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -19314,6 +20144,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121408711</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -19426,6 +20261,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112128923</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19550,6 +20390,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112157771</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19662,6 +20507,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112256644</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -19774,6 +20624,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112256808</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19886,6 +20741,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112308815</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -19988,6 +20848,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112310528</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -20100,6 +20965,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112314464</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -20217,6 +21087,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112493454</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -20335,6 +21210,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128924622</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -20454,6 +21334,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119058605</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -20570,6 +21455,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119058583</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -20686,6 +21576,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119058597</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -20801,6 +21696,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119058664</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -20918,6 +21818,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112157785</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -21015,6 +21920,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119130128</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -21146,6 +22056,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112157798</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -21258,6 +22173,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112157784</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -21369,6 +22289,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119058686</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -21480,6 +22405,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119058687</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -21597,6 +22527,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112257684</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -21704,6 +22639,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112130485</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -21820,6 +22760,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112157761</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -21936,6 +22881,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112157806</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -22052,6 +23002,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112157807</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -22168,6 +23123,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112157804</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -22280,6 +23240,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112129200</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -22390,6 +23355,11 @@
       <c r="AY194" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112309786</t>
         </is>
       </c>
     </row>
@@ -22507,6 +23477,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112130333</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -22617,6 +23592,11 @@
       <c r="AY196" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112130376</t>
         </is>
       </c>
     </row>
@@ -22734,6 +23714,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119058610</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -22839,6 +23824,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119130129</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -22960,6 +23950,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112157789</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -23082,6 +24077,11 @@
       <c r="AY200" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112157797</t>
         </is>
       </c>
     </row>
@@ -23194,6 +24194,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112215252</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -23309,6 +24314,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112257557</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -23411,6 +24421,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112310552</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -23511,6 +24526,11 @@
       <c r="AY204" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112313514</t>
         </is>
       </c>
     </row>
@@ -23628,6 +24648,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112314853</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -23748,6 +24773,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112131422</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -23876,6 +24906,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112160851</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -23978,8 +25013,222 @@
           <t>Värdefull natur i Stockholms län</t>
         </is>
       </c>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131431260</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>